--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:35:29+00:00</t>
+    <t>2026-08-28T09:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:07:16+00:00</t>
+    <t>2026-08-28T12:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:09:44+00:00</t>
+    <t>2026-08-28T12:57:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:57:14+00:00</t>
+    <t>2026-08-28T14:34:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:34:56+00:00</t>
+    <t>2026-08-31T19:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-vent-exspiratorischer-gasfluss.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.3</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:08:04+00:00</t>
+    <t>2026-08-31T19:21:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
